--- a/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-startup-checklist.xlsx
+++ b/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-startup-checklist.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Fish served raw must be frozen before service (FDA Food Code 3-402.11): at −4 °F (−20 °C) or below for 7 days, or at −31 °F (−35 °C) or below until solid and then held 15 hours, or until solid and then held at −4 °F for 24 hours. Tuna species and feed-raised farmed fish such as salmon are exempt with a written statement from the supplier. Your state adopts its own edition of the Code. If you freeze in-house, the freezer and its footprint go into the space plan.</t>
+          <t>Fish served raw must be frozen before service (FDA Food Code 3-402.11): at −4 °F (−20 °C) or below for 7 days, or at −31 °F (−35 °C) or below until solid and then held 15 hours, or until solid and then held at −4 °F for 24 hours. Tuna species are exempt, and so are feed-raised farmed fish such as salmon with a written statement from the supplier or the farmer. Your state adopts its own edition of the Code. If you freeze in-house, the freezer and its footprint go into the space plan.</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Ask your state alcohol beverage control (ABC) agency and your city what they need, and file as soon as you sign the lease. Sake usually falls under the wine license: ask your state ABC. Approval can take months; never open counting on it, and add liquor liability to your insurance.</t>
+          <t>Start in week 1: ask your state alcohol beverage control (ABC) agency and your city what they need, and file as soon as you sign the lease (Phase 2). Sake usually falls under the wine license: ask your state ABC. Approval can take months; never open counting on it, and add liquor liability to your insurance.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Fish served raw or nearly raw (nigiri, sashimi, maki, tartare, poke) must be frozen per Food Code 3-402.11: −4 °F (−20 °C) or below for 7 days, or the −31 °F (−35 °C) options. Tuna species and feed-raised farmed fish such as salmon are exempt with a written supplier statement. For wild fish, farmed yellowtail (hamachi), mackerel (saba) and squid, get the supplier's letter or keep your own freezing log.</t>
+          <t>Fish served raw or nearly raw (nigiri, sashimi, maki, tartare, poke) must be frozen per Food Code 3-402.11: −4 °F (−20 °C) or below for 7 days, or the −31 °F (−35 °C) options. Tuna species are exempt, and so are feed-raised farmed fish such as salmon with a written supplier statement. For wild fish, farmed yellowtail (hamachi), mackerel (saba) and squid, get the supplier's letter or keep your own freezing log.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>If the fish arrives already frozen for raw service, the supplier's letter must say so. For tuna and for feed-raised farmed fish, such as farmed salmon, the exemption needs a written statement from the supplier or the farmer. File them with the lot and keep them 90 days after the fish is served: the inspector asks for them first.</t>
+          <t>If the fish arrives already frozen for raw service, the supplier's letter must say so. For feed-raised farmed fish, such as farmed salmon, the exemption needs a written statement from the supplier or the farmer (3-402.12); for tuna, keep the invoice or letter that names the species. File them with the lot and keep them 90 days after the fish is served: the inspector asks for them first.</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Mark every raw or undercooked item with an asterisk or a description (disclosure) and add the reminder: "Consuming raw or undercooked fish or seafood may increase your risk of foodborne illness" (Food Code 3-603.11). Put both on the menu, on your website and on every marketplace listing.</t>
+          <t>Mark every raw or undercooked item with an asterisk or a description (disclosure) and add the reminder: "Consuming raw or undercooked meats, poultry, seafood, shellfish, or eggs may increase your risk of foodborne illness" (Food Code 3-603.11). Put both on the menu, on your website and on every marketplace listing.</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Hold fish at 41 °F (5 °C) or below, and keep the reach-in for the service fish at 32-34 °F (0-1 °C). Thaw in the walk-in, never at room temperature, and write down when it leaves the freezer.</t>
+          <t>Hold fish at 41 °F (5 °C) or below, and keep the reach-in for the service fish at 32-34 °F (0-1 °C). Thaw in the walk-in, never at room temperature, and write down when it leaves the freezer. Vacuum-packed frozen fish labeled "keep frozen" (saku blocks often are) comes out of its bag before it thaws (Food Code 3-501.13).</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>In the US the owner is the GM and the head sushi chef, who buys, cleans and cuts the fish, is a hire: the hardest one (the example plan pays about $30 per hour, a Kit estimate). Let both weigh in on the sushi bar and the refrigeration before you close the build-out: an absence of the only person who cuts closes the sushi bar.</t>
+          <t>In this plan the owner is the GM, and the head sushi chef, who buys, cleans and cuts the fish, is a hire: the hardest one (the example plan pays about $30 per hour, a Kit estimate). Let both weigh in on the sushi bar and the refrigeration before you close the build-out: an absence of the only person who cuts closes the sushi bar.</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Use the Sushi Fish, Rice &amp; Costing Calculator in the kit: the cost of each piece and the margin in the dining room, for take-out and on the marketplaces. On a marketplace the margin of a platter drops sharply.</t>
+          <t>Use the Sushi Fish, Rice &amp; Costing Calculator in the kit: the cost of each piece and the margin in the dining room, for take-out and on the marketplaces. Even with the higher marketplace price, a platter leaves about a fifth to a quarter less margin there than in the dining room.</t>
         </is>
       </c>
     </row>
